--- a/outputs/dados/dados_api_ipea.xlsx
+++ b/outputs/dados/dados_api_ipea.xlsx
@@ -12393,7 +12393,7 @@
         <v>208131</v>
       </c>
       <c r="D300" t="n">
-        <v>4382704</v>
+        <v>4382025</v>
       </c>
       <c r="E300" t="n">
         <v>617.3643637196692</v>
@@ -12431,7 +12431,7 @@
         <v>178050</v>
       </c>
       <c r="D301" t="n">
-        <v>4428977</v>
+        <v>4430415</v>
       </c>
       <c r="E301" t="n">
         <v>621.5321905391406</v>
@@ -12475,7 +12475,7 @@
         <v>150946</v>
       </c>
       <c r="D302" t="n">
-        <v>4460716</v>
+        <v>4466950</v>
       </c>
       <c r="E302" t="n">
         <v>625.7132375848973</v>
@@ -12512,7 +12512,9 @@
       <c r="C303" t="n">
         <v>193845</v>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="n">
+        <v>4491912</v>
+      </c>
       <c r="E303" t="n">
         <v>629.6007939300123</v>
       </c>
